--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.3984,0.1560,0.1396,0.4135</t>
-  </si>
-  <si>
-    <t>0.0130,0.0074,0.0071,0.9840</t>
-  </si>
-  <si>
-    <t>0.3649,0.1026,0.0266,0.6342</t>
-  </si>
-  <si>
-    <t>0.0752,0.0188,0.0080,0.9562</t>
-  </si>
-  <si>
-    <t>0.9840,0.0185,0.0022,0.0033</t>
-  </si>
-  <si>
-    <t>0.9742,0.0313,0.0046,0.0039</t>
-  </si>
-  <si>
-    <t>0.9761,0.0218,0.0048,0.0048</t>
-  </si>
-  <si>
-    <t>0.9607,0.0410,0.0096,0.0070</t>
-  </si>
-  <si>
-    <t>0.9850,0.0112,0.0024,0.0053</t>
-  </si>
-  <si>
-    <t>0.9490,0.0585,0.0077,0.0100</t>
-  </si>
-  <si>
-    <t>0.9718,0.0337,0.0050,0.0041</t>
-  </si>
-  <si>
-    <t>0.9696,0.0371,0.0061,0.0045</t>
-  </si>
-  <si>
-    <t>0.3403,0.0965,0.6316,0.0389</t>
-  </si>
-  <si>
-    <t>0.1961,0.0636,0.8147,0.0201</t>
-  </si>
-  <si>
-    <t>0.2887,0.0290,0.7089,0.0505</t>
-  </si>
-  <si>
-    <t>0.1372,0.1190,0.8077,0.0118</t>
-  </si>
-  <si>
-    <t>0.4029,0.0594,0.5902,0.0626</t>
-  </si>
-  <si>
-    <t>0.0126,0.9724,0.0761,0.0020</t>
-  </si>
-  <si>
-    <t>0.0311,0.9511,0.0768,0.0041</t>
-  </si>
-  <si>
-    <t>0.1120,0.8320,0.1087,0.0049</t>
-  </si>
-  <si>
-    <t>0.0941,0.9186,0.0406,0.0066</t>
-  </si>
-  <si>
-    <t>0.0114,0.9824,0.0289,0.0015</t>
-  </si>
-  <si>
-    <t>0.3487,0.0613,0.5420,0.0835</t>
-  </si>
-  <si>
-    <t>0.3279,0.0432,0.5550,0.1125</t>
-  </si>
-  <si>
-    <t>0.0599,0.0115,0.8898,0.0632</t>
-  </si>
-  <si>
-    <t>0.2769,0.2305,0.5759,0.0316</t>
-  </si>
-  <si>
-    <t>0.0800,0.0143,0.9495,0.0099</t>
-  </si>
-  <si>
-    <t>0.1002,0.0415,0.8521,0.0511</t>
-  </si>
-  <si>
-    <t>0.0483,0.0158,0.9165,0.0476</t>
-  </si>
-  <si>
-    <t>0.0711,0.9249,0.0500,0.0073</t>
-  </si>
-  <si>
-    <t>0.3126,0.3648,0.3743,0.0203</t>
-  </si>
-  <si>
-    <t>0.0130,0.0334,0.9800,0.0051</t>
-  </si>
-  <si>
-    <t>0.0307,0.8929,0.2226,0.0064</t>
-  </si>
-  <si>
-    <t>0.7929,0.1217,0.0703,0.0638</t>
-  </si>
-  <si>
-    <t>0.1333,0.0647,0.8620,0.0213</t>
-  </si>
-  <si>
-    <t>0.4578,0.6725,0.0261,0.0038</t>
-  </si>
-  <si>
-    <t>0.0266,0.8902,0.3290,0.0023</t>
-  </si>
-  <si>
-    <t>0.0120,0.8061,0.7132,0.0061</t>
-  </si>
-  <si>
-    <t>0.0249,0.3497,0.9011,0.0060</t>
-  </si>
-  <si>
-    <t>0.0562,0.3169,0.8373,0.0110</t>
-  </si>
-  <si>
-    <t>0.2432,0.0774,0.6971,0.0379</t>
-  </si>
-  <si>
-    <t>0.0154,0.4341,0.9032,0.0039</t>
-  </si>
-  <si>
-    <t>0.0055,0.9319,0.4635,0.0030</t>
-  </si>
-  <si>
-    <t>0.0363,0.3163,0.8673,0.0064</t>
-  </si>
-  <si>
-    <t>0.1355,0.3556,0.0420,0.7224</t>
-  </si>
-  <si>
-    <t>0.0047,0.9861,0.0268,0.0027</t>
-  </si>
-  <si>
-    <t>0.0042,0.9813,0.0809,0.0022</t>
-  </si>
-  <si>
-    <t>0.0034,0.9889,0.0443,0.0013</t>
-  </si>
-  <si>
-    <t>0.0125,0.1202,0.9666,0.0033</t>
-  </si>
-  <si>
-    <t>0.0054,0.2295,0.9763,0.0011</t>
-  </si>
-  <si>
-    <t>0.0515,0.0150,0.9684,0.0054</t>
-  </si>
-  <si>
-    <t>0.1180,0.0184,0.8426,0.0547</t>
-  </si>
-  <si>
-    <t>0.0294,0.1113,0.9346,0.0073</t>
-  </si>
-  <si>
-    <t>0.0333,0.0649,0.9458,0.0076</t>
-  </si>
-  <si>
-    <t>0.9429,0.0866,0.0098,0.0034</t>
-  </si>
-  <si>
-    <t>0.9646,0.0449,0.0067,0.0051</t>
-  </si>
-  <si>
-    <t>0.9685,0.0285,0.0030,0.0101</t>
-  </si>
-  <si>
-    <t>0.0210,0.1892,0.9260,0.0031</t>
-  </si>
-  <si>
-    <t>0.9464,0.0743,0.0090,0.0061</t>
-  </si>
-  <si>
-    <t>0.9679,0.0282,0.0069,0.0085</t>
-  </si>
-  <si>
-    <t>0.9339,0.0796,0.0155,0.0084</t>
-  </si>
-  <si>
-    <t>0.0029,0.9224,0.7041,0.0012</t>
-  </si>
-  <si>
-    <t>0.0068,0.1239,0.9784,0.0023</t>
-  </si>
-  <si>
-    <t>0.0117,0.0187,0.9861,0.0028</t>
-  </si>
-  <si>
-    <t>0.0062,0.5780,0.9203,0.0026</t>
-  </si>
-  <si>
-    <t>0.0062,0.0046,0.9881,0.0067</t>
-  </si>
-  <si>
-    <t>0.0122,0.9734,0.0525,0.0030</t>
-  </si>
-  <si>
-    <t>0.0015,0.9933,0.0281,0.0009</t>
-  </si>
-  <si>
-    <t>0.5952,0.3715,0.1255,0.0342</t>
-  </si>
-  <si>
-    <t>0.4768,0.5436,0.0881,0.0176</t>
-  </si>
-  <si>
-    <t>0.0303,0.4025,0.8014,0.0152</t>
-  </si>
-  <si>
-    <t>0.0036,0.7779,0.8574,0.0010</t>
-  </si>
-  <si>
-    <t>0.0186,0.4577,0.8866,0.0038</t>
-  </si>
-  <si>
-    <t>0.0022,0.9589,0.4922,0.0012</t>
-  </si>
-  <si>
-    <t>0.0053,0.8468,0.7751,0.0025</t>
-  </si>
-  <si>
-    <t>0.0478,0.0273,0.0662,0.9057</t>
-  </si>
-  <si>
-    <t>0.0034,0.0056,0.0008,0.9967</t>
-  </si>
-  <si>
-    <t>0.0073,0.0076,0.0029,0.9916</t>
-  </si>
-  <si>
-    <t>0.0123,0.0160,0.0042,0.9876</t>
-  </si>
-  <si>
-    <t>0.0527,0.0772,0.0703,0.8993</t>
-  </si>
-  <si>
-    <t>0.0468,0.0637,0.0183,0.9500</t>
-  </si>
-  <si>
-    <t>0.0054,0.9040,0.6527,0.0026</t>
-  </si>
-  <si>
-    <t>0.0068,0.5912,0.9257,0.0016</t>
-  </si>
-  <si>
-    <t>0.0146,0.6656,0.8346,0.0046</t>
-  </si>
-  <si>
-    <t>0.0127,0.2670,0.9492,0.0034</t>
-  </si>
-  <si>
-    <t>0.0091,0.7835,0.7869,0.0024</t>
-  </si>
-  <si>
-    <t>0.0085,0.8466,0.6781,0.0036</t>
-  </si>
-  <si>
-    <t>0.9513,0.0710,0.0086,0.0051</t>
-  </si>
-  <si>
-    <t>0.9638,0.0431,0.0052,0.0057</t>
-  </si>
-  <si>
-    <t>0.9398,0.1016,0.0086,0.0040</t>
-  </si>
-  <si>
-    <t>0.9437,0.0877,0.0110,0.0042</t>
-  </si>
-  <si>
-    <t>0.9777,0.0229,0.0041,0.0052</t>
-  </si>
-  <si>
-    <t>0.9733,0.0251,0.0044,0.0071</t>
-  </si>
-  <si>
-    <t>0.9760,0.0243,0.0045,0.0051</t>
-  </si>
-  <si>
-    <t>0.9702,0.0389,0.0045,0.0040</t>
-  </si>
-  <si>
-    <t>0.9807,0.0169,0.0036,0.0049</t>
-  </si>
-  <si>
-    <t>0.9807,0.0178,0.0032,0.0051</t>
-  </si>
-  <si>
-    <t>0.9747,0.0350,0.0043,0.0030</t>
-  </si>
-  <si>
-    <t>0.9833,0.0173,0.0020,0.0046</t>
-  </si>
-  <si>
-    <t>0.9736,0.0306,0.0040,0.0056</t>
-  </si>
-  <si>
-    <t>0.9475,0.0676,0.0129,0.0060</t>
-  </si>
-  <si>
-    <t>0.9749,0.0308,0.0039,0.0042</t>
-  </si>
-  <si>
-    <t>0.9443,0.0649,0.0122,0.0083</t>
-  </si>
-  <si>
-    <t>0.0012,0.0038,0.9975,0.0011</t>
-  </si>
-  <si>
-    <t>0.1079,0.0222,0.9296,0.0081</t>
-  </si>
-  <si>
-    <t>0.4356,0.0795,0.3144,0.2233</t>
-  </si>
-  <si>
-    <t>0.1003,0.0398,0.9081,0.0086</t>
-  </si>
-  <si>
-    <t>0.0184,0.9697,0.0521,0.0019</t>
-  </si>
-  <si>
-    <t>0.0230,0.9704,0.0419,0.0022</t>
-  </si>
-  <si>
-    <t>0.0332,0.9656,0.0241,0.0032</t>
-  </si>
-  <si>
-    <t>0.0859,0.9249,0.0396,0.0053</t>
-  </si>
-  <si>
-    <t>0.0321,0.9600,0.0506,0.0032</t>
-  </si>
-  <si>
-    <t>0.0421,0.9518,0.0474,0.0037</t>
-  </si>
-  <si>
-    <t>0.1906,0.8231,0.0498,0.0066</t>
-  </si>
-  <si>
-    <t>0.4254,0.4377,0.2214,0.0616</t>
-  </si>
-  <si>
-    <t>0.1472,0.0117,0.8374,0.0662</t>
-  </si>
-  <si>
-    <t>0.1290,0.6585,0.3137,0.0114</t>
-  </si>
-  <si>
-    <t>0.3383,0.0949,0.6097,0.0769</t>
-  </si>
-  <si>
-    <t>0.6473,0.1158,0.1822,0.1085</t>
-  </si>
-  <si>
-    <t>0.0022,0.9920,0.0355,0.0010</t>
-  </si>
-  <si>
-    <t>0.0067,0.9716,0.0889,0.0045</t>
-  </si>
-  <si>
-    <t>0.0499,0.9231,0.1003,0.0079</t>
-  </si>
-  <si>
-    <t>0.0005,0.9962,0.0343,0.0005</t>
-  </si>
-  <si>
-    <t>0.1014,0.8840,0.0816,0.0044</t>
-  </si>
-  <si>
-    <t>0.4432,0.6574,0.0408,0.0064</t>
-  </si>
-  <si>
-    <t>0.3705,0.6863,0.0498,0.0056</t>
-  </si>
-  <si>
-    <t>0.9402,0.0472,0.0139,0.0162</t>
-  </si>
-  <si>
-    <t>0.9490,0.0261,0.0071,0.0284</t>
-  </si>
-  <si>
-    <t>0.9684,0.0284,0.0046,0.0084</t>
-  </si>
-  <si>
-    <t>0.9400,0.0412,0.0120,0.0226</t>
-  </si>
-  <si>
-    <t>0.9666,0.0259,0.0070,0.0101</t>
-  </si>
-  <si>
-    <t>0.9382,0.0421,0.0181,0.0196</t>
-  </si>
-  <si>
-    <t>0.9471,0.0598,0.0117,0.0079</t>
-  </si>
-  <si>
-    <t>0.9495,0.0397,0.0059,0.0158</t>
-  </si>
-  <si>
-    <t>0.0172,0.1387,0.9618,0.0031</t>
-  </si>
-  <si>
-    <t>0.0165,0.2072,0.9483,0.0019</t>
-  </si>
-  <si>
-    <t>0.0093,0.3925,0.9227,0.0024</t>
-  </si>
-  <si>
-    <t>0.0553,0.2056,0.8705,0.0157</t>
-  </si>
-  <si>
-    <t>0.1248,0.0557,0.2411,0.6772</t>
-  </si>
-  <si>
-    <t>0.3072,0.4534,0.2923,0.0813</t>
-  </si>
-  <si>
-    <t>0.2241,0.0305,0.8303,0.0258</t>
-  </si>
-  <si>
-    <t>0.3985,0.4736,0.1911,0.0359</t>
-  </si>
-  <si>
-    <t>0.0390,0.0111,0.0066,0.9725</t>
-  </si>
-  <si>
-    <t>0.0012,0.0037,0.0010,0.9976</t>
-  </si>
-  <si>
-    <t>0.0046,0.0171,0.0046,0.9902</t>
-  </si>
-  <si>
-    <t>0.0052,0.0075,0.0020,0.9941</t>
-  </si>
-  <si>
-    <t>0.0034,0.8203,0.8385,0.0015</t>
-  </si>
-  <si>
-    <t>0.9304,0.0652,0.0176,0.0124</t>
-  </si>
-  <si>
-    <t>0.6196,0.3711,0.0851,0.0295</t>
-  </si>
-  <si>
-    <t>0.9243,0.0812,0.0119,0.0150</t>
-  </si>
-  <si>
-    <t>0.8168,0.2716,0.0175,0.0081</t>
-  </si>
-  <si>
-    <t>0.9108,0.0671,0.0290,0.0193</t>
-  </si>
-  <si>
-    <t>0.3616,0.0619,0.1048,0.5790</t>
-  </si>
-  <si>
-    <t>0.9510,0.0386,0.0088,0.0159</t>
-  </si>
-  <si>
-    <t>0.0199,0.0247,0.9701,0.0096</t>
-  </si>
-  <si>
-    <t>0.7149,0.0482,0.0361,0.2345</t>
-  </si>
-  <si>
-    <t>0.7895,0.1267,0.1048,0.0233</t>
-  </si>
-  <si>
-    <t>0.1584,0.8214,0.0702,0.0121</t>
-  </si>
-  <si>
-    <t>0.7143,0.3738,0.0338,0.0163</t>
-  </si>
-  <si>
-    <t>0.7654,0.2740,0.0417,0.0170</t>
-  </si>
-  <si>
-    <t>0.3632,0.6646,0.0761,0.0201</t>
-  </si>
-  <si>
-    <t>0.5606,0.3434,0.1566,0.0755</t>
-  </si>
-  <si>
-    <t>0.4102,0.6263,0.0650,0.0152</t>
-  </si>
-  <si>
-    <t>0.9758,0.0210,0.0042,0.0072</t>
-  </si>
-  <si>
-    <t>0.9401,0.0756,0.0093,0.0091</t>
-  </si>
-  <si>
-    <t>0.9567,0.0400,0.0113,0.0091</t>
-  </si>
-  <si>
-    <t>0.9632,0.0190,0.0055,0.0217</t>
-  </si>
-  <si>
-    <t>0.9580,0.0424,0.0108,0.0069</t>
-  </si>
-  <si>
-    <t>0.9652,0.0198,0.0052,0.0160</t>
-  </si>
-  <si>
-    <t>0.9584,0.0329,0.0107,0.0115</t>
-  </si>
-  <si>
-    <t>0.9397,0.0668,0.0095,0.0109</t>
-  </si>
-  <si>
-    <t>0.1472,0.8743,0.0495,0.0079</t>
-  </si>
-  <si>
-    <t>0.6120,0.4891,0.0276,0.0060</t>
-  </si>
-  <si>
-    <t>0.1841,0.8290,0.0470,0.0070</t>
-  </si>
-  <si>
-    <t>0.4488,0.0786,0.6026,0.0143</t>
-  </si>
-  <si>
-    <t>0.7610,0.2762,0.0446,0.0149</t>
-  </si>
-  <si>
-    <t>0.7153,0.2811,0.0669,0.0210</t>
-  </si>
-  <si>
-    <t>0.8994,0.1301,0.0201,0.0078</t>
-  </si>
-  <si>
-    <t>0.8054,0.2304,0.0425,0.0151</t>
-  </si>
-  <si>
-    <t>0.0180,0.0518,0.9715,0.0019</t>
-  </si>
-  <si>
-    <t>0.7924,0.2583,0.0331,0.0122</t>
-  </si>
-  <si>
-    <t>0.0197,0.0136,0.9744,0.0078</t>
-  </si>
-  <si>
-    <t>0.0222,0.0567,0.9671,0.0038</t>
-  </si>
-  <si>
-    <t>0.1547,0.3905,0.5494,0.0227</t>
-  </si>
-  <si>
-    <t>0.0302,0.1090,0.9487,0.0039</t>
-  </si>
-  <si>
-    <t>0.0171,0.0233,0.9823,0.0026</t>
-  </si>
-  <si>
-    <t>0.0357,0.0155,0.9685,0.0096</t>
-  </si>
-  <si>
-    <t>0.0161,0.0115,0.9890,0.0020</t>
-  </si>
-  <si>
-    <t>0.4153,0.2891,0.3544,0.0498</t>
-  </si>
-  <si>
-    <t>0.1677,0.1023,0.7946,0.0150</t>
-  </si>
-  <si>
-    <t>0.6028,0.1755,0.1993,0.0831</t>
-  </si>
-  <si>
-    <t>0.2730,0.2804,0.4883,0.0180</t>
-  </si>
-  <si>
-    <t>0.2102,0.0970,0.7477,0.0309</t>
-  </si>
-  <si>
-    <t>0.2280,0.2755,0.5405,0.0213</t>
-  </si>
-  <si>
-    <t>0.3767,0.2094,0.4643,0.0333</t>
-  </si>
-  <si>
-    <t>0.4723,0.3308,0.2462,0.0254</t>
-  </si>
-  <si>
-    <t>0.3453,0.7511,0.0232,0.0049</t>
-  </si>
-  <si>
-    <t>0.8514,0.2402,0.0125,0.0050</t>
-  </si>
-  <si>
-    <t>0.9059,0.1450,0.0152,0.0054</t>
-  </si>
-  <si>
-    <t>0.9305,0.0971,0.0134,0.0078</t>
-  </si>
-  <si>
-    <t>0.7236,0.4073,0.0199,0.0069</t>
-  </si>
-  <si>
-    <t>0.4580,0.1377,0.4143,0.0468</t>
-  </si>
-  <si>
-    <t>0.5941,0.1516,0.2825,0.0559</t>
-  </si>
-  <si>
-    <t>0.3604,0.0476,0.1307,0.5196</t>
-  </si>
-  <si>
-    <t>0.3449,0.2084,0.5165,0.0326</t>
-  </si>
-  <si>
-    <t>0.5363,0.0878,0.4005,0.0591</t>
-  </si>
-  <si>
-    <t>0.0300,0.0205,0.9707,0.0055</t>
-  </si>
-  <si>
-    <t>0.1446,0.2348,0.7125,0.0325</t>
-  </si>
-  <si>
-    <t>0.0827,0.0998,0.8848,0.0278</t>
-  </si>
-  <si>
-    <t>0.0478,0.2622,0.8767,0.0143</t>
-  </si>
-  <si>
-    <t>0.0122,0.7936,0.7736,0.0049</t>
-  </si>
-  <si>
-    <t>0.9713,0.0303,0.0058,0.0056</t>
-  </si>
-  <si>
-    <t>0.9426,0.0723,0.0109,0.0066</t>
-  </si>
-  <si>
-    <t>0.9729,0.0304,0.0070,0.0032</t>
-  </si>
-  <si>
-    <t>0.9355,0.1019,0.0086,0.0054</t>
-  </si>
-  <si>
-    <t>0.9386,0.1002,0.0092,0.0048</t>
-  </si>
-  <si>
-    <t>0.9616,0.0557,0.0072,0.0032</t>
-  </si>
-  <si>
-    <t>0.9722,0.0325,0.0051,0.0040</t>
-  </si>
-  <si>
-    <t>0.9464,0.0393,0.0156,0.0153</t>
-  </si>
-  <si>
-    <t>0.1622,0.0461,0.8722,0.0253</t>
-  </si>
-  <si>
-    <t>0.4455,0.2905,0.3003,0.0120</t>
-  </si>
-  <si>
-    <t>0.8070,0.2185,0.0447,0.0189</t>
-  </si>
-  <si>
-    <t>0.0229,0.0112,0.9799,0.0047</t>
-  </si>
-  <si>
-    <t>0.0104,0.0161,0.9841,0.0043</t>
-  </si>
-  <si>
-    <t>0.0424,0.2423,0.8760,0.0079</t>
-  </si>
-  <si>
-    <t>0.0063,0.0034,0.9861,0.0101</t>
-  </si>
-  <si>
-    <t>0.1827,0.0442,0.8147,0.0312</t>
-  </si>
-  <si>
-    <t>0.0049,0.0199,0.9909,0.0021</t>
-  </si>
-  <si>
-    <t>0.0581,0.0656,0.9287,0.0096</t>
-  </si>
-  <si>
-    <t>0.1358,0.5314,0.4466,0.0127</t>
-  </si>
-  <si>
-    <t>0.4144,0.0598,0.2870,0.2681</t>
-  </si>
-  <si>
-    <t>0.4005,0.0955,0.5368,0.0719</t>
-  </si>
-  <si>
-    <t>0.2836,0.0372,0.1566,0.5364</t>
-  </si>
-  <si>
-    <t>0.9266,0.1137,0.0122,0.0053</t>
-  </si>
-  <si>
-    <t>0.9618,0.0470,0.0056,0.0064</t>
-  </si>
-  <si>
-    <t>0.9604,0.0492,0.0080,0.0053</t>
-  </si>
-  <si>
-    <t>0.9787,0.0189,0.0031,0.0053</t>
-  </si>
-  <si>
-    <t>0.9548,0.0427,0.0107,0.0095</t>
-  </si>
-  <si>
-    <t>0.9752,0.0300,0.0033,0.0046</t>
-  </si>
-  <si>
-    <t>0.9851,0.0199,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.9647,0.0490,0.0076,0.0038</t>
-  </si>
-  <si>
-    <t>0.0601,0.0452,0.9394,0.0066</t>
-  </si>
-  <si>
-    <t>0.0068,0.0284,0.9903,0.0013</t>
-  </si>
-  <si>
-    <t>0.0476,0.0853,0.9427,0.0047</t>
-  </si>
-  <si>
-    <t>0.1545,0.3883,0.5696,0.0099</t>
-  </si>
-  <si>
-    <t>0.0033,0.0040,0.9936,0.0037</t>
-  </si>
-  <si>
-    <t>0.2374,0.0339,0.7070,0.0731</t>
-  </si>
-  <si>
-    <t>0.1464,0.0132,0.6333,0.1958</t>
-  </si>
-  <si>
-    <t>0.0989,0.0828,0.8289,0.0501</t>
-  </si>
-  <si>
-    <t>0.4795,0.0246,0.0182,0.6526</t>
-  </si>
-  <si>
-    <t>0.0312,0.0549,0.0213,0.9537</t>
-  </si>
-  <si>
-    <t>0.0325,0.0232,0.0036,0.9793</t>
-  </si>
-  <si>
-    <t>0.0063,0.0053,0.0018,0.9945</t>
-  </si>
-  <si>
-    <t>0.0075,0.0110,0.0019,0.9932</t>
-  </si>
-  <si>
-    <t>0.3766,0.1278,0.0713,0.5558</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.5225,0.1009,0.0671,0.4023</t>
+  </si>
+  <si>
+    <t>0.0396,0.0134,0.0084,0.9710</t>
+  </si>
+  <si>
+    <t>0.4999,0.1112,0.0413,0.4573</t>
+  </si>
+  <si>
+    <t>0.3810,0.1086,0.0480,0.6079</t>
+  </si>
+  <si>
+    <t>0.9664,0.0379,0.0067,0.0063</t>
+  </si>
+  <si>
+    <t>0.9826,0.0107,0.0019,0.0079</t>
+  </si>
+  <si>
+    <t>0.9729,0.0189,0.0058,0.0096</t>
+  </si>
+  <si>
+    <t>0.9760,0.0155,0.0058,0.0078</t>
+  </si>
+  <si>
+    <t>0.9768,0.0249,0.0039,0.0041</t>
+  </si>
+  <si>
+    <t>0.9849,0.0148,0.0023,0.0038</t>
+  </si>
+  <si>
+    <t>0.9764,0.0205,0.0038,0.0060</t>
+  </si>
+  <si>
+    <t>0.9574,0.0448,0.0105,0.0071</t>
+  </si>
+  <si>
+    <t>0.3437,0.2507,0.4433,0.0249</t>
+  </si>
+  <si>
+    <t>0.4732,0.2163,0.3198,0.0485</t>
+  </si>
+  <si>
+    <t>0.1927,0.0287,0.8677,0.0092</t>
+  </si>
+  <si>
+    <t>0.0795,0.0275,0.9387,0.0130</t>
+  </si>
+  <si>
+    <t>0.1846,0.2017,0.6544,0.0106</t>
+  </si>
+  <si>
+    <t>0.0198,0.9619,0.0747,0.0031</t>
+  </si>
+  <si>
+    <t>0.0592,0.9368,0.0549,0.0038</t>
+  </si>
+  <si>
+    <t>0.1238,0.8596,0.0752,0.0058</t>
+  </si>
+  <si>
+    <t>0.0395,0.9443,0.0660,0.0046</t>
+  </si>
+  <si>
+    <t>0.0028,0.9916,0.0439,0.0005</t>
+  </si>
+  <si>
+    <t>0.4862,0.0610,0.4258,0.0862</t>
+  </si>
+  <si>
+    <t>0.1790,0.0252,0.5064,0.2744</t>
+  </si>
+  <si>
+    <t>0.0323,0.0071,0.9464,0.0258</t>
+  </si>
+  <si>
+    <t>0.3160,0.1024,0.5968,0.0850</t>
+  </si>
+  <si>
+    <t>0.1715,0.0353,0.8638,0.0179</t>
+  </si>
+  <si>
+    <t>0.0557,0.0063,0.8545,0.1142</t>
+  </si>
+  <si>
+    <t>0.0100,0.0067,0.9842,0.0088</t>
+  </si>
+  <si>
+    <t>0.1197,0.7727,0.1816,0.0121</t>
+  </si>
+  <si>
+    <t>0.4251,0.3778,0.2365,0.0188</t>
+  </si>
+  <si>
+    <t>0.0155,0.0362,0.9764,0.0050</t>
+  </si>
+  <si>
+    <t>0.0266,0.9374,0.1044,0.0079</t>
+  </si>
+  <si>
+    <t>0.7692,0.2029,0.0451,0.0561</t>
+  </si>
+  <si>
+    <t>0.2661,0.6737,0.1244,0.0195</t>
+  </si>
+  <si>
+    <t>0.3913,0.6639,0.0467,0.0056</t>
+  </si>
+  <si>
+    <t>0.0197,0.9180,0.2595,0.0027</t>
+  </si>
+  <si>
+    <t>0.0180,0.7901,0.6822,0.0084</t>
+  </si>
+  <si>
+    <t>0.0644,0.1211,0.8879,0.0164</t>
+  </si>
+  <si>
+    <t>0.0253,0.4593,0.8668,0.0063</t>
+  </si>
+  <si>
+    <t>0.3029,0.0951,0.5834,0.0995</t>
+  </si>
+  <si>
+    <t>0.0373,0.4402,0.8116,0.0076</t>
+  </si>
+  <si>
+    <t>0.0025,0.9709,0.2760,0.0021</t>
+  </si>
+  <si>
+    <t>0.0576,0.0797,0.9276,0.0065</t>
+  </si>
+  <si>
+    <t>0.1453,0.3837,0.0380,0.6578</t>
+  </si>
+  <si>
+    <t>0.0091,0.9680,0.0669,0.0065</t>
+  </si>
+  <si>
+    <t>0.0033,0.9843,0.0879,0.0020</t>
+  </si>
+  <si>
+    <t>0.0059,0.9839,0.0641,0.0015</t>
+  </si>
+  <si>
+    <t>0.0044,0.6947,0.9029,0.0017</t>
+  </si>
+  <si>
+    <t>0.0057,0.2933,0.9663,0.0011</t>
+  </si>
+  <si>
+    <t>0.0973,0.0372,0.8957,0.0236</t>
+  </si>
+  <si>
+    <t>0.0406,0.0087,0.9722,0.0083</t>
+  </si>
+  <si>
+    <t>0.0116,0.0361,0.9797,0.0039</t>
+  </si>
+  <si>
+    <t>0.0199,0.0384,0.9674,0.0057</t>
+  </si>
+  <si>
+    <t>0.9758,0.0325,0.0040,0.0028</t>
+  </si>
+  <si>
+    <t>0.9420,0.0514,0.0153,0.0116</t>
+  </si>
+  <si>
+    <t>0.9478,0.0634,0.0121,0.0057</t>
+  </si>
+  <si>
+    <t>0.0320,0.0646,0.9526,0.0070</t>
+  </si>
+  <si>
+    <t>0.9625,0.0516,0.0064,0.0043</t>
+  </si>
+  <si>
+    <t>0.9539,0.0545,0.0102,0.0076</t>
+  </si>
+  <si>
+    <t>0.9072,0.1232,0.0156,0.0087</t>
+  </si>
+  <si>
+    <t>0.0028,0.9020,0.7901,0.0011</t>
+  </si>
+  <si>
+    <t>0.0052,0.1898,0.9799,0.0013</t>
+  </si>
+  <si>
+    <t>0.0258,0.0594,0.9319,0.0226</t>
+  </si>
+  <si>
+    <t>0.0036,0.9325,0.6544,0.0018</t>
+  </si>
+  <si>
+    <t>0.0047,0.0114,0.9918,0.0023</t>
+  </si>
+  <si>
+    <t>0.0086,0.9683,0.1166,0.0027</t>
+  </si>
+  <si>
+    <t>0.0010,0.9956,0.0145,0.0007</t>
+  </si>
+  <si>
+    <t>0.5100,0.0741,0.4899,0.0257</t>
+  </si>
+  <si>
+    <t>0.2647,0.6336,0.1528,0.0186</t>
+  </si>
+  <si>
+    <t>0.0374,0.4263,0.7335,0.0147</t>
+  </si>
+  <si>
+    <t>0.0055,0.8043,0.8134,0.0013</t>
+  </si>
+  <si>
+    <t>0.0099,0.7164,0.8390,0.0019</t>
+  </si>
+  <si>
+    <t>0.0018,0.9674,0.4378,0.0016</t>
+  </si>
+  <si>
+    <t>0.0018,0.9495,0.6585,0.0007</t>
+  </si>
+  <si>
+    <t>0.1431,0.0125,0.0554,0.8183</t>
+  </si>
+  <si>
+    <t>0.0074,0.0061,0.0013,0.9944</t>
+  </si>
+  <si>
+    <t>0.0127,0.0176,0.0063,0.9845</t>
+  </si>
+  <si>
+    <t>0.0823,0.0405,0.0288,0.9235</t>
+  </si>
+  <si>
+    <t>0.0126,0.0102,0.0219,0.9696</t>
+  </si>
+  <si>
+    <t>0.0051,0.0265,0.0030,0.9916</t>
+  </si>
+  <si>
+    <t>0.0022,0.9357,0.7211,0.0010</t>
+  </si>
+  <si>
+    <t>0.0050,0.8336,0.8071,0.0017</t>
+  </si>
+  <si>
+    <t>0.0242,0.4374,0.8827,0.0070</t>
+  </si>
+  <si>
+    <t>0.0260,0.0710,0.9561,0.0061</t>
+  </si>
+  <si>
+    <t>0.0022,0.9665,0.4124,0.0012</t>
+  </si>
+  <si>
+    <t>0.0170,0.7537,0.7224,0.0057</t>
+  </si>
+  <si>
+    <t>0.9812,0.0216,0.0031,0.0032</t>
+  </si>
+  <si>
+    <t>0.9784,0.0273,0.0028,0.0034</t>
+  </si>
+  <si>
+    <t>0.9771,0.0292,0.0033,0.0033</t>
+  </si>
+  <si>
+    <t>0.9609,0.0506,0.0075,0.0052</t>
+  </si>
+  <si>
+    <t>0.9772,0.0236,0.0033,0.0050</t>
+  </si>
+  <si>
+    <t>0.9834,0.0152,0.0024,0.0043</t>
+  </si>
+  <si>
+    <t>0.9557,0.0454,0.0107,0.0085</t>
+  </si>
+  <si>
+    <t>0.9859,0.0134,0.0020,0.0034</t>
+  </si>
+  <si>
+    <t>0.9749,0.0144,0.0047,0.0103</t>
+  </si>
+  <si>
+    <t>0.9800,0.0193,0.0037,0.0050</t>
+  </si>
+  <si>
+    <t>0.9328,0.0993,0.0121,0.0061</t>
+  </si>
+  <si>
+    <t>0.9674,0.0288,0.0078,0.0080</t>
+  </si>
+  <si>
+    <t>0.9754,0.0288,0.0048,0.0037</t>
+  </si>
+  <si>
+    <t>0.9676,0.0371,0.0053,0.0063</t>
+  </si>
+  <si>
+    <t>0.9770,0.0226,0.0038,0.0051</t>
+  </si>
+  <si>
+    <t>0.8577,0.1649,0.0356,0.0122</t>
+  </si>
+  <si>
+    <t>0.0178,0.0181,0.9701,0.0128</t>
+  </si>
+  <si>
+    <t>0.1089,0.0570,0.8920,0.0109</t>
+  </si>
+  <si>
+    <t>0.3028,0.1425,0.2497,0.4626</t>
+  </si>
+  <si>
+    <t>0.2924,0.1246,0.5729,0.0719</t>
+  </si>
+  <si>
+    <t>0.0268,0.9601,0.0586,0.0031</t>
+  </si>
+  <si>
+    <t>0.0132,0.9739,0.0542,0.0016</t>
+  </si>
+  <si>
+    <t>0.1030,0.8859,0.0654,0.0073</t>
+  </si>
+  <si>
+    <t>0.2485,0.7596,0.0745,0.0092</t>
+  </si>
+  <si>
+    <t>0.0070,0.9795,0.0827,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.9927,0.0235,0.0007</t>
+  </si>
+  <si>
+    <t>0.5710,0.5399,0.0273,0.0071</t>
+  </si>
+  <si>
+    <t>0.1170,0.8349,0.1143,0.0192</t>
+  </si>
+  <si>
+    <t>0.1343,0.0652,0.8642,0.0213</t>
+  </si>
+  <si>
+    <t>0.5364,0.1557,0.3138,0.0514</t>
+  </si>
+  <si>
+    <t>0.3809,0.3063,0.3711,0.0311</t>
+  </si>
+  <si>
+    <t>0.4086,0.4412,0.1977,0.0868</t>
+  </si>
+  <si>
+    <t>0.0153,0.9658,0.0596,0.0045</t>
+  </si>
+  <si>
+    <t>0.0041,0.9845,0.0397,0.0034</t>
+  </si>
+  <si>
+    <t>0.1170,0.8164,0.1229,0.0134</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.0344,0.0004</t>
+  </si>
+  <si>
+    <t>0.0389,0.9304,0.1100,0.0028</t>
+  </si>
+  <si>
+    <t>0.3583,0.6079,0.0902,0.0082</t>
+  </si>
+  <si>
+    <t>0.1639,0.8595,0.0513,0.0051</t>
+  </si>
+  <si>
+    <t>0.9665,0.0331,0.0078,0.0064</t>
+  </si>
+  <si>
+    <t>0.9474,0.0534,0.0130,0.0097</t>
+  </si>
+  <si>
+    <t>0.9557,0.0378,0.0099,0.0112</t>
+  </si>
+  <si>
+    <t>0.8824,0.1249,0.0344,0.0186</t>
+  </si>
+  <si>
+    <t>0.9479,0.0575,0.0103,0.0093</t>
+  </si>
+  <si>
+    <t>0.9218,0.0753,0.0172,0.0177</t>
+  </si>
+  <si>
+    <t>0.9753,0.0216,0.0044,0.0057</t>
+  </si>
+  <si>
+    <t>0.9662,0.0249,0.0072,0.0115</t>
+  </si>
+  <si>
+    <t>0.0080,0.4212,0.9400,0.0019</t>
+  </si>
+  <si>
+    <t>0.0089,0.6349,0.8678,0.0014</t>
+  </si>
+  <si>
+    <t>0.0296,0.2100,0.9169,0.0041</t>
+  </si>
+  <si>
+    <t>0.0515,0.1495,0.9031,0.0061</t>
+  </si>
+  <si>
+    <t>0.3806,0.5488,0.1176,0.0950</t>
+  </si>
+  <si>
+    <t>0.6339,0.1944,0.2120,0.0266</t>
+  </si>
+  <si>
+    <t>0.4382,0.0643,0.5804,0.0467</t>
+  </si>
+  <si>
+    <t>0.4365,0.1511,0.4457,0.0640</t>
+  </si>
+  <si>
+    <t>0.0210,0.0142,0.0055,0.9825</t>
+  </si>
+  <si>
+    <t>0.0012,0.0046,0.0011,0.9974</t>
+  </si>
+  <si>
+    <t>0.0059,0.0154,0.0049,0.9892</t>
+  </si>
+  <si>
+    <t>0.0024,0.0052,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0079,0.7719,0.7999,0.0029</t>
+  </si>
+  <si>
+    <t>0.9207,0.0874,0.0179,0.0151</t>
+  </si>
+  <si>
+    <t>0.8934,0.1232,0.0184,0.0187</t>
+  </si>
+  <si>
+    <t>0.9079,0.0919,0.0188,0.0210</t>
+  </si>
+  <si>
+    <t>0.7285,0.3557,0.0329,0.0103</t>
+  </si>
+  <si>
+    <t>0.8729,0.1370,0.0284,0.0182</t>
+  </si>
+  <si>
+    <t>0.6264,0.0314,0.1221,0.2228</t>
+  </si>
+  <si>
+    <t>0.9360,0.0363,0.0147,0.0305</t>
+  </si>
+  <si>
+    <t>0.0212,0.0629,0.9575,0.0087</t>
+  </si>
+  <si>
+    <t>0.4363,0.0371,0.0254,0.6438</t>
+  </si>
+  <si>
+    <t>0.8850,0.0429,0.0246,0.0626</t>
+  </si>
+  <si>
+    <t>0.1701,0.8286,0.0642,0.0153</t>
+  </si>
+  <si>
+    <t>0.5662,0.5223,0.0434,0.0177</t>
+  </si>
+  <si>
+    <t>0.3914,0.6411,0.0814,0.0221</t>
+  </si>
+  <si>
+    <t>0.1992,0.7798,0.0726,0.0310</t>
+  </si>
+  <si>
+    <t>0.3477,0.6148,0.1067,0.0145</t>
+  </si>
+  <si>
+    <t>0.4081,0.5601,0.1238,0.0181</t>
+  </si>
+  <si>
+    <t>0.9570,0.0271,0.0076,0.0156</t>
+  </si>
+  <si>
+    <t>0.9581,0.0323,0.0068,0.0149</t>
+  </si>
+  <si>
+    <t>0.9697,0.0350,0.0050,0.0057</t>
+  </si>
+  <si>
+    <t>0.9630,0.0258,0.0044,0.0151</t>
+  </si>
+  <si>
+    <t>0.9476,0.0440,0.0110,0.0136</t>
+  </si>
+  <si>
+    <t>0.9292,0.0892,0.0100,0.0090</t>
+  </si>
+  <si>
+    <t>0.9763,0.0181,0.0027,0.0092</t>
+  </si>
+  <si>
+    <t>0.9599,0.0438,0.0082,0.0071</t>
+  </si>
+  <si>
+    <t>0.1794,0.7515,0.1364,0.0141</t>
+  </si>
+  <si>
+    <t>0.7883,0.3498,0.0140,0.0056</t>
+  </si>
+  <si>
+    <t>0.1297,0.8601,0.0715,0.0062</t>
+  </si>
+  <si>
+    <t>0.2574,0.0766,0.7753,0.0106</t>
+  </si>
+  <si>
+    <t>0.9148,0.1317,0.0130,0.0038</t>
+  </si>
+  <si>
+    <t>0.8794,0.1529,0.0234,0.0096</t>
+  </si>
+  <si>
+    <t>0.9108,0.1373,0.0148,0.0046</t>
+  </si>
+  <si>
+    <t>0.5200,0.5761,0.0231,0.0216</t>
+  </si>
+  <si>
+    <t>0.0092,0.0737,0.9782,0.0011</t>
+  </si>
+  <si>
+    <t>0.8657,0.1538,0.0270,0.0161</t>
+  </si>
+  <si>
+    <t>0.0108,0.0104,0.9869,0.0043</t>
+  </si>
+  <si>
+    <t>0.0256,0.1509,0.9385,0.0055</t>
+  </si>
+  <si>
+    <t>0.1648,0.0814,0.8158,0.0137</t>
+  </si>
+  <si>
+    <t>0.0089,0.2473,0.9622,0.0022</t>
+  </si>
+  <si>
+    <t>0.0117,0.0138,0.9889,0.0013</t>
+  </si>
+  <si>
+    <t>0.0135,0.0288,0.9808,0.0020</t>
+  </si>
+  <si>
+    <t>0.0225,0.0360,0.9736,0.0037</t>
+  </si>
+  <si>
+    <t>0.2866,0.1799,0.5725,0.0163</t>
+  </si>
+  <si>
+    <t>0.3275,0.3134,0.3816,0.0251</t>
+  </si>
+  <si>
+    <t>0.3154,0.5728,0.1812,0.0129</t>
+  </si>
+  <si>
+    <t>0.0613,0.9176,0.0672,0.0106</t>
+  </si>
+  <si>
+    <t>0.0429,0.8524,0.2845,0.0059</t>
+  </si>
+  <si>
+    <t>0.3363,0.2387,0.4432,0.0928</t>
+  </si>
+  <si>
+    <t>0.4464,0.1373,0.4878,0.0201</t>
+  </si>
+  <si>
+    <t>0.4104,0.2561,0.4046,0.0283</t>
+  </si>
+  <si>
+    <t>0.4798,0.6703,0.0233,0.0047</t>
+  </si>
+  <si>
+    <t>0.8535,0.2328,0.0137,0.0054</t>
+  </si>
+  <si>
+    <t>0.9443,0.0710,0.0129,0.0065</t>
+  </si>
+  <si>
+    <t>0.9469,0.0819,0.0086,0.0042</t>
+  </si>
+  <si>
+    <t>0.4862,0.5849,0.0309,0.0080</t>
+  </si>
+  <si>
+    <t>0.2857,0.4011,0.3791,0.0496</t>
+  </si>
+  <si>
+    <t>0.2799,0.6786,0.1476,0.0167</t>
+  </si>
+  <si>
+    <t>0.4329,0.0876,0.3797,0.1977</t>
+  </si>
+  <si>
+    <t>0.5713,0.1310,0.3240,0.0571</t>
+  </si>
+  <si>
+    <t>0.4462,0.0558,0.5513,0.0474</t>
+  </si>
+  <si>
+    <t>0.0479,0.0393,0.9121,0.0500</t>
+  </si>
+  <si>
+    <t>0.0914,0.2433,0.8009,0.0309</t>
+  </si>
+  <si>
+    <t>0.0435,0.4562,0.8089,0.0151</t>
+  </si>
+  <si>
+    <t>0.0536,0.0998,0.9034,0.0163</t>
+  </si>
+  <si>
+    <t>0.0554,0.1219,0.9159,0.0077</t>
+  </si>
+  <si>
+    <t>0.9686,0.0272,0.0063,0.0093</t>
+  </si>
+  <si>
+    <t>0.9469,0.0627,0.0075,0.0087</t>
+  </si>
+  <si>
+    <t>0.9807,0.0202,0.0032,0.0043</t>
+  </si>
+  <si>
+    <t>0.9655,0.0463,0.0086,0.0030</t>
+  </si>
+  <si>
+    <t>0.9579,0.0597,0.0073,0.0054</t>
+  </si>
+  <si>
+    <t>0.9756,0.0350,0.0040,0.0031</t>
+  </si>
+  <si>
+    <t>0.9824,0.0189,0.0021,0.0040</t>
+  </si>
+  <si>
+    <t>0.9301,0.0768,0.0158,0.0108</t>
+  </si>
+  <si>
+    <t>0.1481,0.0413,0.8782,0.0287</t>
+  </si>
+  <si>
+    <t>0.1127,0.7246,0.2138,0.0060</t>
+  </si>
+  <si>
+    <t>0.7998,0.1673,0.0798,0.0304</t>
+  </si>
+  <si>
+    <t>0.0260,0.0105,0.9756,0.0074</t>
+  </si>
+  <si>
+    <t>0.0120,0.0292,0.9791,0.0059</t>
+  </si>
+  <si>
+    <t>0.0549,0.0704,0.9279,0.0081</t>
+  </si>
+  <si>
+    <t>0.0049,0.0285,0.9928,0.0007</t>
+  </si>
+  <si>
+    <t>0.0867,0.0856,0.8978,0.0102</t>
+  </si>
+  <si>
+    <t>0.0029,0.0303,0.9933,0.0011</t>
+  </si>
+  <si>
+    <t>0.0408,0.0235,0.9694,0.0041</t>
+  </si>
+  <si>
+    <t>0.0902,0.2080,0.7894,0.0092</t>
+  </si>
+  <si>
+    <t>0.6252,0.0676,0.2908,0.0586</t>
+  </si>
+  <si>
+    <t>0.2530,0.0284,0.3095,0.4140</t>
+  </si>
+  <si>
+    <t>0.7054,0.0416,0.1229,0.1133</t>
+  </si>
+  <si>
+    <t>0.7769,0.3166,0.0211,0.0065</t>
+  </si>
+  <si>
+    <t>0.9708,0.0361,0.0034,0.0057</t>
+  </si>
+  <si>
+    <t>0.9212,0.0920,0.0151,0.0138</t>
+  </si>
+  <si>
+    <t>0.9561,0.0514,0.0104,0.0067</t>
+  </si>
+  <si>
+    <t>0.9517,0.0417,0.0115,0.0112</t>
+  </si>
+  <si>
+    <t>0.9050,0.1487,0.0119,0.0064</t>
+  </si>
+  <si>
+    <t>0.9766,0.0251,0.0046,0.0044</t>
+  </si>
+  <si>
+    <t>0.9331,0.0963,0.0125,0.0065</t>
+  </si>
+  <si>
+    <t>0.0575,0.2297,0.8491,0.0095</t>
+  </si>
+  <si>
+    <t>0.0202,0.0745,0.9638,0.0040</t>
+  </si>
+  <si>
+    <t>0.0219,0.2880,0.9198,0.0048</t>
+  </si>
+  <si>
+    <t>0.1000,0.1314,0.8432,0.0097</t>
+  </si>
+  <si>
+    <t>0.0206,0.0141,0.9748,0.0077</t>
+  </si>
+  <si>
+    <t>0.1659,0.0369,0.8329,0.0404</t>
+  </si>
+  <si>
+    <t>0.3272,0.0388,0.6823,0.0335</t>
+  </si>
+  <si>
+    <t>0.0558,0.0309,0.9145,0.0331</t>
+  </si>
+  <si>
+    <t>0.4852,0.0112,0.0062,0.7030</t>
+  </si>
+  <si>
+    <t>0.0052,0.0133,0.0074,0.9874</t>
+  </si>
+  <si>
+    <t>0.0315,0.0159,0.0082,0.9764</t>
+  </si>
+  <si>
+    <t>0.0107,0.0058,0.0032,0.9905</t>
+  </si>
+  <si>
+    <t>0.0023,0.0040,0.0007,0.9974</t>
+  </si>
+  <si>
+    <t>0.3581,0.2389,0.0937,0.4683</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2631,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4129,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4171,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4185,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4398,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5207,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
